--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_valparaiso.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:37</t>
+    <t xml:space="preserve">2026-09-09 20:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezjov_a_2021_valparaiso.xlsx
@@ -24,114 +24,114 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Fernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Pascua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Algarrobo</t>
   </si>
   <si>
-    <t xml:space="preserve">Cabildo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Larga</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
-    <t xml:space="preserve">Casablanca</t>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Tabo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
     <t xml:space="preserve">Catemu</t>
   </si>
   <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Quisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Tabo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hijuelas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Pascua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Fernandez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
   </si>
   <si>
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Olmué</t>
   </si>
   <si>
-    <t xml:space="preserve">Panquehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puchuncaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilpué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinconada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Felipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
-    <t xml:space="preserve">Viña del Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zapallar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:39</t>
+    <t xml:space="preserve">2026-09-18 10:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -553,7 +553,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.04</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +569,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.32</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="5">
@@ -577,7 +577,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.15</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.34</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.47</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="10">
@@ -617,7 +617,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.88</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="11">
@@ -625,7 +625,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="12">
@@ -633,7 +633,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="13">
@@ -641,7 +641,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="15">
@@ -657,7 +657,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="16">
@@ -665,7 +665,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>3.97</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="17">
@@ -673,7 +673,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3.02</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="18">
@@ -681,7 +681,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="19">
@@ -689,7 +689,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3.8</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="20">
@@ -697,7 +697,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="21">
@@ -705,7 +705,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -713,7 +713,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1.47</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="23">
@@ -721,7 +721,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>4.72</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="24">
@@ -729,7 +729,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>3.78</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="25">
@@ -737,7 +737,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="26">
@@ -745,7 +745,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3.37</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="27">
@@ -753,7 +753,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>4.74</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="28">
@@ -761,7 +761,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="29">
@@ -769,7 +769,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2.77</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="30">
@@ -777,7 +777,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2.87</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="31">
@@ -785,7 +785,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3.59</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="32">
@@ -793,7 +793,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>4.09</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="33">
@@ -801,7 +801,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2.08</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="34">
@@ -809,7 +809,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>3.93</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="35">
@@ -817,7 +817,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>3.64</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="36">
@@ -825,7 +825,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="37">
@@ -833,7 +833,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2.51</v>
+        <v>3.64</v>
       </c>
     </row>
   </sheetData>
